--- a/src/assets/template.xlsx
+++ b/src/assets/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\company project\automation\src\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78CA84E4-C88E-4828-A35F-512757A6FE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6FC0E5-CD49-4440-B8D0-1BA5C340B04D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{1DD955D2-EF45-9048-A5A6-E89058C7550A}"/>
+    <workbookView xWindow="4692" yWindow="2676" windowWidth="17280" windowHeight="8880" firstSheet="1" activeTab="1" xr2:uid="{1DD955D2-EF45-9048-A5A6-E89058C7550A}"/>
   </bookViews>
   <sheets>
     <sheet name="LR" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="PDPT" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'ARUS KAS'!$A$1:$C$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'ARUS KAS'!$A$1:$C$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">LR!$A$1:$C$22</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">PDPT!$A$1:$C$9</definedName>
   </definedNames>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>URAIAN</t>
   </si>
@@ -312,6 +312,12 @@
   </si>
   <si>
     <t>Cadangan Kerugian Piutang Usaha Pihak Ketiga</t>
+  </si>
+  <si>
+    <t>Revaluasi asset tetap</t>
+  </si>
+  <si>
+    <t>Buyback saham Perkumpulan LPP</t>
   </si>
 </sst>
 </file>
@@ -445,7 +451,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -561,13 +567,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -658,6 +675,9 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1166,7 +1186,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54.36328125" customWidth="1"/>
@@ -1224,13 +1244,13 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.6" thickBot="1">
-      <c r="A8" s="23" t="s">
-        <v>88</v>
+      <c r="A8" s="35" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.6" thickBot="1">
       <c r="A9" s="23" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.6" thickBot="1">
@@ -1279,27 +1299,32 @@
       </c>
     </row>
     <row r="19" spans="1:1" ht="15.6" thickBot="1">
-      <c r="A19" s="24" t="s">
-        <v>74</v>
+      <c r="A19" s="23" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15.6" thickBot="1">
       <c r="A20" s="24" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15.6" thickBot="1">
       <c r="A21" s="24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="15.6" thickBot="1">
+      <c r="A22" s="24" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="15.6" thickBot="1">
-      <c r="A22" s="23" t="s">
+    <row r="23" spans="1:1" ht="15.6" thickBot="1">
+      <c r="A23" s="23" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="15.6" thickBot="1">
-      <c r="A23" s="24" t="s">
+    <row r="24" spans="1:1" ht="15.6" thickBot="1">
+      <c r="A24" s="24" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1308,13 +1333,13 @@
     <mergeCell ref="A1:A3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="58" orientation="portrait" horizontalDpi="4294967292" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="58" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69274188-6643-4074-8AE6-3C9C471C3A7C}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.453125" customWidth="1"/>
@@ -1591,17 +1616,22 @@
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.6" thickBot="1">
-      <c r="A39" s="27" t="s">
+      <c r="A39" s="28" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15.6" thickBot="1">
+      <c r="A40" s="27" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.6" thickBot="1">
-      <c r="A40" s="29" t="s">
+    <row r="41" spans="1:3" ht="15.6" thickBot="1">
+      <c r="A41" s="29" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.6" thickBot="1">
-      <c r="A41" s="30" t="s">
+    <row r="42" spans="1:3" ht="15.6" thickBot="1">
+      <c r="A42" s="30" t="s">
         <v>82</v>
       </c>
     </row>
